--- a/docs/video_manual/v1.6/demo_database/appdata/uploads/masters/MASTER-0001.xlsx
+++ b/docs/video_manual/v1.6/demo_database/appdata/uploads/masters/MASTER-0001.xlsx
@@ -5460,11 +5460,6 @@
           <t>PER_BOX</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>CG04-AB-1002</t>
